--- a/3d_Printed_Frames/UCF_08/UCF_08_Hardware.xlsx
+++ b/3d_Printed_Frames/UCF_08/UCF_08_Hardware.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RoseEngine\GitHub\3DPrinted_Working\UCF_08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692753F0-53BC-415D-8617-E120EC17C08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF93A661-E784-4BCA-913B-F423E3D96F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2835" yWindow="540" windowWidth="23955" windowHeight="15000" xr2:uid="{5CFBD7AF-40A2-4737-8D61-F203D56443D1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Qty</t>
   </si>
@@ -78,6 +78,30 @@
   </si>
   <si>
     <t>M4 nut (may use a square nut)</t>
+  </si>
+  <si>
+    <t>M5x set screw</t>
+  </si>
+  <si>
+    <t>Main Body</t>
+  </si>
+  <si>
+    <t>Insert Cutterhead</t>
+  </si>
+  <si>
+    <t>TDHB07T1202</t>
+  </si>
+  <si>
+    <t>M2.2x6 insert machine screw</t>
+  </si>
+  <si>
+    <t>Round Cutter Cutterhead</t>
+  </si>
+  <si>
+    <t>M3x6 or M3x8 set screw</t>
+  </si>
+  <si>
+    <t>1/8" cutter</t>
   </si>
 </sst>
 </file>
@@ -136,14 +160,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -480,89 +510,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0CC435D-A945-4593-8148-762F9392005D}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:3" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -570,15 +599,15 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,12 +615,75 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
